--- a/TestData/remote.xlsx
+++ b/TestData/remote.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,23 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>v11_R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>k13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>v13_R_modified</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>v13_R_modified</t>
         </is>
       </c>
     </row>
